--- a/InFiRA-QA/834770-QA.xlsx
+++ b/InFiRA-QA/834770-QA.xlsx
@@ -1031,7 +1031,7 @@
         <v>11</v>
       </c>
       <c r="B30" s="9">
-        <v>9.42</v>
+        <v>9.39</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>6</v>
